--- a/artfynd/A 5417-2026 artfynd.xlsx
+++ b/artfynd/A 5417-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128989748</v>
+        <v>128989743</v>
       </c>
       <c r="B2" t="n">
-        <v>86981</v>
+        <v>87322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512668</v>
+        <v>512651</v>
       </c>
       <c r="R2" t="n">
-        <v>6695135</v>
+        <v>6695149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -809,36 +809,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128989756</v>
+        <v>128989748</v>
       </c>
       <c r="B3" t="n">
-        <v>86950</v>
+        <v>87322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>248955</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -935,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128989743</v>
+        <v>68151248</v>
       </c>
       <c r="B4" t="n">
-        <v>86981</v>
+        <v>92886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,45 +954,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1988</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högbergsån, Dlr</t>
+          <t>Nedere Högbergsåravinen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512651</v>
+        <v>512624</v>
       </c>
       <c r="R4" t="n">
-        <v>6695149</v>
+        <v>6695162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2017-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,47 +1026,157 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Hedblandskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>kontinuitetsskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Kontinuitetsskog i erosionsraviner</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Anders Janols</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Janols, Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128989756</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högbergsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512668</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6695135</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>kontinuitetsskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Janolof Hermansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
